--- a/output/details/2026-05-25/preprocessed_data.xlsx
+++ b/output/details/2026-05-25/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46167</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1149694049459753</v>
+        <v>-0.1199932349818361</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1495560167636684</v>
+        <v>-0.1390984822150189</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1493518773330542</v>
+        <v>-0.1388255819844693</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1183198701996563</v>
+        <v>0.003695663613518787</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001698172781392302</v>
+        <v>0.001694279129038689</v>
       </c>
       <c r="G2" t="n">
-        <v>1.943343736739088</v>
+        <v>2.503814147051636</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4411871973788583</v>
+        <v>-0.2723212113704103</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
